--- a/templates_formats/sabana de notas.xlsx
+++ b/templates_formats/sabana de notas.xlsx
@@ -103,9 +103,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -157,15 +172,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -195,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -217,44 +223,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="20"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="24"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="27"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="20"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,111 +539,216 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC54"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="2" width="3.25" customWidth="1"/>
-    <col min="3" max="3" width="10.125" customWidth="1"/>
-    <col min="4" max="4" width="31.375" customWidth="1"/>
-    <col min="5" max="29" width="2.75" customWidth="1"/>
+    <col min="1" max="1" width="0.25" customWidth="1"/>
+    <col min="2" max="2" width="2.875" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="33.875" customWidth="1"/>
+    <col min="5" max="28" width="2.875" customWidth="1"/>
+    <col min="29" max="29" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D1" s="16" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-    </row>
-    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D2" s="17" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-    </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D3" s="18" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-    </row>
-    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D4" s="19" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="X4" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D5" s="10" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-    </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D6" s="13" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-    </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>5</v>
       </c>
@@ -672,8 +759,11 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="U7" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>6</v>
       </c>
@@ -685,17 +775,32 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="D9" s="15"/>
-      <c r="E9" s="2" t="s">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="D9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="G10" s="2"/>
@@ -704,67 +809,67 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:28" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="20" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="20" t="s">
+      <c r="H11" s="12"/>
+      <c r="I11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="20" t="s">
+      <c r="J11" s="12"/>
+      <c r="K11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="21"/>
-      <c r="M11" s="20" t="s">
+      <c r="L11" s="12"/>
+      <c r="M11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="21"/>
-      <c r="O11" s="20" t="s">
+      <c r="N11" s="12"/>
+      <c r="O11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="20" t="s">
+      <c r="P11" s="12"/>
+      <c r="Q11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="R11" s="21"/>
-      <c r="S11" s="20" t="s">
+      <c r="R11" s="12"/>
+      <c r="S11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="T11" s="21"/>
-      <c r="U11" s="20" t="s">
+      <c r="T11" s="12"/>
+      <c r="U11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="V11" s="21"/>
-      <c r="W11" s="20" t="s">
+      <c r="V11" s="12"/>
+      <c r="W11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="20" t="s">
+      <c r="X11" s="12"/>
+      <c r="Y11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="20" t="s">
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" s="21"/>
-    </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="AB11" s="12"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -840,7 +945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>1</v>
       </c>
@@ -871,7 +976,7 @@
       <c r="AA13" s="6"/>
       <c r="AB13" s="6"/>
     </row>
-    <row r="14" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>2</v>
       </c>
@@ -902,7 +1007,7 @@
       <c r="AA14" s="6"/>
       <c r="AB14" s="6"/>
     </row>
-    <row r="15" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>3</v>
       </c>
@@ -933,7 +1038,7 @@
       <c r="AA15" s="6"/>
       <c r="AB15" s="6"/>
     </row>
-    <row r="16" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>4</v>
       </c>
@@ -1460,7 +1565,7 @@
       <c r="AA32" s="6"/>
       <c r="AB32" s="6"/>
     </row>
-    <row r="33" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <v>21</v>
       </c>
@@ -1491,7 +1596,7 @@
       <c r="AA33" s="6"/>
       <c r="AB33" s="6"/>
     </row>
-    <row r="34" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <v>22</v>
       </c>
@@ -1522,7 +1627,7 @@
       <c r="AA34" s="6"/>
       <c r="AB34" s="6"/>
     </row>
-    <row r="35" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <v>23</v>
       </c>
@@ -1553,7 +1658,7 @@
       <c r="AA35" s="6"/>
       <c r="AB35" s="6"/>
     </row>
-    <row r="36" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <v>24</v>
       </c>
@@ -1584,657 +1689,190 @@
       <c r="AA36" s="6"/>
       <c r="AB36" s="6"/>
     </row>
-    <row r="37" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="5">
-        <v>25</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="6"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="6"/>
-      <c r="Y37" s="6"/>
-      <c r="Z37" s="6"/>
-      <c r="AA37" s="6"/>
-      <c r="AB37" s="6"/>
-    </row>
-    <row r="38" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="5">
-        <v>26</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="6"/>
-      <c r="AA38" s="6"/>
-      <c r="AB38" s="6"/>
-    </row>
-    <row r="39" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="5">
-        <v>27</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="6"/>
-      <c r="AB39" s="6"/>
-    </row>
-    <row r="40" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="5">
-        <v>28</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6"/>
-      <c r="W40" s="6"/>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="6"/>
-      <c r="Z40" s="6"/>
-      <c r="AA40" s="6"/>
-      <c r="AB40" s="6"/>
-    </row>
-    <row r="41" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="5">
-        <v>29</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6"/>
-      <c r="AA41" s="6"/>
-      <c r="AB41" s="6"/>
-    </row>
-    <row r="42" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="5">
-        <v>30</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="6"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="6"/>
-      <c r="AB42" s="6"/>
-    </row>
-    <row r="43" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="5">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="6"/>
-      <c r="AB43" s="6"/>
-    </row>
-    <row r="44" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="5">
-        <v>32</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="6"/>
-      <c r="Y44" s="6"/>
-      <c r="Z44" s="6"/>
-      <c r="AA44" s="6"/>
-      <c r="AB44" s="6"/>
-    </row>
-    <row r="45" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="5">
-        <v>33</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
-      <c r="V45" s="6"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="6"/>
-      <c r="AA45" s="6"/>
-      <c r="AB45" s="6"/>
-    </row>
-    <row r="46" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="5">
-        <v>34</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="6"/>
-      <c r="AB46" s="6"/>
-    </row>
-    <row r="47" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="5">
-        <v>35</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="6"/>
-      <c r="Z47" s="6"/>
-      <c r="AA47" s="6"/>
-      <c r="AB47" s="6"/>
-    </row>
-    <row r="48" spans="2:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="5">
-        <v>36</v>
-      </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
-      <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
-      <c r="V48" s="6"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="6"/>
-      <c r="Z48" s="6"/>
-      <c r="AA48" s="6"/>
-      <c r="AB48" s="6"/>
-    </row>
-    <row r="49" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="5">
-        <v>37</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6"/>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="6"/>
-      <c r="AA49" s="6"/>
-      <c r="AB49" s="6"/>
-    </row>
-    <row r="50" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="5">
-        <v>38</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="6"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="6"/>
-      <c r="AB50" s="6"/>
-    </row>
-    <row r="51" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="9"/>
+    <row r="37" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+    </row>
+    <row r="38" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="P40" s="2"/>
+    </row>
+    <row r="41" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="P41" s="2"/>
+    </row>
+    <row r="42" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="P42" s="2"/>
+    </row>
+    <row r="43" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="P43" s="2"/>
+    </row>
+    <row r="44" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="P44" s="2"/>
+    </row>
+    <row r="45" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="P45" s="2"/>
+    </row>
+    <row r="46" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="P46" s="2"/>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="P48" s="2"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="P49" s="2"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-    </row>
-    <row r="52" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="8"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-    </row>
-    <row r="53" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="8"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-    </row>
-    <row r="54" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="8"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.25">
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="2"/>
-    </row>
-    <row r="55" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="P55" s="2"/>
-    </row>
-    <row r="56" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="P56" s="2"/>
-    </row>
-    <row r="57" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="P57" s="2"/>
-    </row>
-    <row r="58" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="P58" s="2"/>
-    </row>
-    <row r="59" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="P59" s="2"/>
-    </row>
-    <row r="60" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="P60" s="2"/>
-    </row>
-    <row r="61" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="P61" s="2"/>
-    </row>
-    <row r="62" spans="1:28" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="P62" s="2"/>
-    </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="P63" s="2"/>
-    </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="P64" s="2"/>
-    </row>
-    <row r="65" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="P65" s="2"/>
-    </row>
-    <row r="66" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-    </row>
-    <row r="67" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="F70" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="AA11:AB11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G11:H11"/>
@@ -2247,6 +1885,13 @@
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="D9:X9"/>
+    <mergeCell ref="A6:AC6"/>
+    <mergeCell ref="A5:AC5"/>
+    <mergeCell ref="A4:AC4"/>
+    <mergeCell ref="A3:AC3"/>
+    <mergeCell ref="A2:AC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
